--- a/Hilti_Roles_Tracker.xlsx
+++ b/Hilti_Roles_Tracker.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fit Map" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Roles'!$A$3:$N$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Roles'!$A$3:$O$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,6 +153,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -163,6 +166,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -258,9 +264,9 @@
     <author>Tracker</author>
   </authors>
   <commentList>
-    <comment ref="B8" authorId="0" shapeId="0">
+    <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>Paste the roles you are interested in from here down, one per row.</t>
+        <t>Paste any further roles from here down, one per row.</t>
       </text>
     </comment>
   </commentList>
@@ -556,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C28"/>
+  <dimension ref="B2:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -574,7 +580,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Abir Hilal Khan  |  prepared 31.08.2026  |  referral: Timur (Hilti, CFO track)</t>
+          <t>Abir Hilal Khan  |  updated 31.08.2026 with Abir's own role list  |  referral: Timur (Hilti, CFO track)</t>
         </is>
       </c>
     </row>
@@ -604,7 +610,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="52" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>1. Roles (this file)</t>
@@ -612,11 +618,11 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>The 'Roles' sheet is pre-filled with the Hilti roles found by research. It is a DRAFT: Abir will paste the full list of roles they are interested in, and rows get added/edited then. Nothing goes to Timur before that pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+          <t>Abir's six pasted roles are merged in, researched, and ranked with a suggested priority; two researched add-ons are marked 'Suggested' in the List column. Open items before sign-off: verify each live posting, and identify which country 17676-en recruits for (not resolvable from search).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>2. CV</t>
@@ -624,11 +630,11 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Re-tailored to the Hilti CFO track and rebuilt: 'Abir Hilal Khan_CV_Hilti.pdf' in the same repo. One page, ATS-audited, FP&amp;A/controlling vocabulary, 'Internationally mobile' header line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
+          <t>Tailored to the Hilti finance routes and rebuilt: 'Abir Hilal Khan_CV_Hilti.pdf'. One page, ATS-audited. The header now reads 'No visa sponsorship required in Germany' - the unscoped claim would be false for the Schaan, Copenhagen and Vienna roles on this list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
       <c r="B11" s="4" t="inlineStr">
         <is>
           <t>3. Intro message</t>
@@ -636,7 +642,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Deliberately not drafted yet - per plan it is written only once the roles list and the CV are signed off. Facts still needed for it: exact availability (MSc ends 12.2026 -&gt; full-time from 01.2027?), notice/thesis constraints, and preferred start date.</t>
+          <t>Deliberately not drafted yet - written only once (1) and (2) are signed off. Facts still needed: exact availability (MSc ends 12.2026 -&gt; full-time from 01.2027?), citizenship / current work-permit type (drives the Schaan and Copenhagen rows), and which route Timur's own 'CFO track' is.</t>
         </is>
       </c>
     </row>
@@ -650,126 +656,150 @@
     <row r="14" ht="28" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Yellow cells</t>
+          <t>List column</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Yours to edit: Priority, Status, Next Step - and the empty yellow rows on 'Roles', where you paste the roles you are interested in (one row per job ID).</t>
+          <t>'Your list' = the six postings Abir pasted on 31.08.2026. 'Suggested' = add-ons from research worth considering; delete the rows if not wanted.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Status column</t>
+          <t>Yellow cells</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Has a dropdown: Draft - verify posting / Shortlisted / Sent to Timur / Applied / Interview / Offer / Closed - Rejected / On hold.</t>
+          <t>Yours to edit: Priority, Status, Next Step - and the empty yellow rows, where more roles can be pasted (one row per job ID).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>Status column</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Has a dropdown: Draft - verify posting / Shortlisted / Sent to Timur / Applied / Interview / Offer / Closed - Rejected / On hold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
           <t>Fit Map sheet</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Maps every criterion Hilti screens on to the evidence in Abir's profile and where it sits on the CV - useful for the Timur message and for interview prep.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Data caveat - read before forwarding anything</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="B19" s="6" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Two flags that cut across the list</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="78" customHeight="1">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Schaan work permits</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Both m/f/x trainee roles (19052-en finance, 18688-en operations) sit at Global HQ in Schaan, Liechtenstein. Hilti's Schaan trainee postings state that non-EU/EFTA citizens must declare their eligibility to work in Switzerland/Liechtenstein and that employment cannot be guaranteed if no valid permit is obtained. Denmark (16399-en) likewise needs its own permit - a German residence permit does not transfer. Confirm citizenship/permit facts before Timur forwards anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Verify live postings</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>careers.hilti.group was not reachable from the session that built this file (network proxy), so every posting detail here is compiled from search-engine results and Stepstone listings dated 31.08.2026. Job IDs, titles and requirements MUST be checked against the live posting - or confirmed with Timur - before the list is sent anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>careers.hilti.group and hilti.com are blocked from this build environment, so every posting detail is compiled from search-engine results and job boards dated 31.08.2026. Job IDs, titles, locations and requirements MUST be checked against the live posting - or confirmed with Timur - before the list is sent anywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Also seen, deliberately not tracked</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
+    <row r="24" ht="40" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Senior variants</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>'Senior Controller - CFO Track' (16512-de shows both Controller and Senior Controller titles in listings) and 'Join our Talent Community - Senior Controller' (wd-0032949-en, a talent pool, not a live role) - both likely above the experience band.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Where the track leads</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>'CFO Austria with development target to Global CFO career' (19359-en) - far too senior to apply to, but useful proof of what the CFO track is designed to feed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>'Senior Controller - CFO Track' (16512-de shows both Controller and Senior Controller titles in listings) and 'Join our Talent Community - Senior Controller' (wd-0032949-en, a talent pool, not a live role) - both above the experience band.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Newer posting twins</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Several of Abir's IDs have newer siblings that may be the ones actually accepting applications: 48571-en (Schaan finance track), 46350-en (Schaan operations track), 57529-de (Germany business track). Check which ID is live when verifying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Quick stats</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Roles tracked</t>
         </is>
       </c>
-      <c r="C26" s="5">
+      <c r="C28" s="5">
         <f>COUNTA(Roles!B4:B40)</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Sent to Timur</t>
         </is>
       </c>
-      <c r="C27" s="5">
-        <f>COUNTIF(Roles!K4:K40,"Sent to Timur")</f>
+      <c r="C29" s="5">
+        <f>COUNTIF(Roles!L4:L40,"Sent to Timur")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Applied</t>
         </is>
       </c>
-      <c r="C28" s="5">
-        <f>COUNTIF(Roles!K4:K40,"Applied")</f>
+      <c r="C30" s="5">
+        <f>COUNTIF(Roles!L4:L40,"Applied")</f>
         <v/>
       </c>
     </row>
@@ -784,29 +814,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="38" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Hilti - target roles (draft: pre-filled by research 31.08.2026; paste your own roles in the yellow rows; verify every posting live before sending to Timur)</t>
+          <t>Hilti - target roles. 'Your list' rows are the six postings Abir pasted on 31.08.2026; 'Suggested' rows are research add-ons. Priorities are a recommendation - re-rank freely. Verify every posting live before sending to Timur.</t>
         </is>
       </c>
     </row>
@@ -823,60 +854,65 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
           <t>Job ID</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Entity / Location</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Responsibilities / Program Structure</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>Requirements (screening)</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>Languages</t>
-        </is>
-      </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
+          <t>Languages &amp; Permits</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
           <t>Why Abir Fits</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Gaps / To Clarify</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>Next Step</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>Posting URL</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="O3" s="8" t="inlineStr">
         <is>
           <t>Source &amp; Verified</t>
         </is>
@@ -890,365 +926,701 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
+          <t>Global Trainee Program - Outperformer Finance Track (m/f/x)</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Your list</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>19052-en</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Hilti AG - Global HQ, Schaan, Liechtenstein (m/f/x Schaan posting family)</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>24-month global graduate program, HQ-based trainee variant (fixed intake - confirm date)</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Two finance-track options built around Hilti Finance fundamentals plus strategic project assignments: customer-facing exposure and Controlling &amp; Reporting; option 2 rotates Accounting &amp; Shared Services (3-6 mo) -&gt; Controlling &amp; Reporting (6-9 mo) -&gt; Credit &amp; Collection (3 mo). Introductory global summit at HQ with the Executive Board, a 7-day social-project summit abroad, a leadership course at a top European business school, dedicated mentor, sustained senior-management exposure.</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>Recent or soon-completing Master's; roughly 6-30 months of initial professional experience (internships count); fluent English plus at least one other language; globally mobile; leadership potential. Assessment Center at HQ in Liechtenstein.</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>English posting; German valuable day-to-day at a German-speaking HQ. PERMIT: Schaan trainee postings require non-EU/EFTA citizens to declare Swiss/Liechtenstein work eligibility; employment not guaranteed without a permit.</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>The closest role on the list to the Group-CFO ambition: HQ finance trainee. Experience window fits exactly (~19 months across A&amp;M, TCG, Biome, SCAILE). Finance toolkit on the page: scenario and sensitivity modelling, KPI reporting and dashboards, commercial due diligence. Three fluent languages plus German B1; internationally mobile.</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>CH/LI permit path if non-EU citizen - the make-or-break fact for this row. German B1 at a German-speaking HQ. Intake timing vs 12.2026 graduation.</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Draft - verify posting</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Verify live (newer sibling 48571-en may be the open one). Ask Timur how non-EU hires in his cohort handled the permit, and whether the next intake fits a 01.2027 start.</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>https://careers.hilti.group/en/jobs/19052-en/global-trainee-program-outperformer-finance-track-m-f-x/</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>careers.hilti.group via search 31.08.2026; Schaan location and permit warning read from the same m/f/x posting family (18692-en, 19103-en, 46350-en, 48571-en). Verify live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="79.59999999999999" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Outperformer - Global Management Development Program (Finance Track)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Your list</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>17676-en</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Country NOT identifiable from search - nearby IDs are Dubai postings (17449-en business track); open the live posting to confirm</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>24-month rotational graduate program, finance track (per-country home organisation)</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>Standard GMDP finance-track structure: a customer-facing Account Manager year in the home organisation, finance projects at home and abroad, and a Controlling &amp; Reporting rotation; IMD Lausanne leadership journey with qualification; global summits in Schaan with the Executive Board.</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>Master's; 6-30 months initial professional experience; at least 6 months international experience; fluent English plus one other language; globally mobile.</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Depends entirely on the home country this posting recruits for - identify it before ranking. Permit needs follow the country.</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>Same finance-track fit story as row 1; whether it belongs at P1 depends on the country (work rights + language for the sales year).</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>The recruiting country is the single most important unknown on this list - everything else about the row follows from it.</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>Draft - verify posting</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>Open the posting; record country, language and intake; then re-rank this row.</t>
+        </is>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>https://careers.hilti.group/en/jobs/17676-en/outperformer-global-management-development-program-finance-track/</t>
+        </is>
+      </c>
+      <c r="O5" s="17" t="inlineStr">
+        <is>
+          <t>ID not resolvable via search 31.08.2026 (careers.hilti.group blocked); structure inferred from the GMDP finance-track family. Verify live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92.2" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Outperformer - Global Management Development Program, Business Track</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Your list</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>19580-de</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Hilti Deutschland AG - Deutschlandweit</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>24-month rotational graduate program (German posting; fixed intake - confirm date)</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>General-management twin of the finance track: sales-led rotations starting with an Account Manager year, project rotations including an international assignment; IMD Lausanne leadership journey; global summits in Schaan with the Executive Board.</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>Master's; early-career experience window; fluent English plus one other language; globally mobile; leadership potential.</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>German posting - working German expected for the DACH sales year (B1 is the risk to probe). Germany: no visa sponsorship needed per the prior CVs - the safest permit position on the list.</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>Strongest commercial evidence on the CV (owned North American clients, signed &gt;$100k ARR); Munich home base; zero permit friction. Route back to finance runs through later internal moves - Hilti promotes cross-functionally.</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>Not finance-specialised, so it trades track fit for feasibility. German level for selling.</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>Draft - verify posting</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>Ask Timur how realistic a B1-German sales year is in the German org, and whether business-track entrants later cross into finance.</t>
+        </is>
+      </c>
+      <c r="N6" s="14" t="inlineStr">
+        <is>
+          <t>https://careers.hilti.group/en/jobs/19580-de/global-management-development-program-outperformer-business-track/</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>careers.hilti.group via search 31.08.2026 - 19580-de itself did not surface; twins 19157-de and 57529-de did. Verify live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="117.4" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
           <t>Controller (m/f/d) - International Finance Career / CFO Track</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>16066-en (EN); German twin 16512-de</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Suggested</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>16066-en; DE twin 16512-de</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>Hilti Deutschland AG - Central Europe finance hub, Kaufering, Bavaria (~50 km west of Munich)</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Direct entry, permanent, full-time (Stepstone lists a home-office option)</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Support the Central Europe region across the whole Financial Performance Management process: monthly and annual closings, rolling forecasts, cost controlling and business partnering. Cross-functional and international project assignments. Explicitly built as the entry point of Hilti's CFO track - development via international assignments toward Group CFO-level roles.</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Degree in Business Administration / Economics or similar, ideally with a Finance, Controlling or Accounting focus. Relevant internships and/or up to 3 years' experience in a corporate finance function, an audit firm or consulting. Conceptual strength, stakeholder management, international career ambition.</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>Posting runs in English and German. English is the hub working language; German helps for DACH business partnering - ask Timur what level the team expects.</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>MSc Finance at Nova SBE (FT #8, top 10%) + finance &amp; strategy bachelor's (magna cum laude). A&amp;M restructuring = consulting-grade corporate finance at Fortune 500 scale. Scenario models and EBITDA sensitivity analysis map to forecasting / cost controlling. KPI reporting and dashboards at SCAILE map to controlling &amp; reporting. 90+ stakeholder interviews at TCG. Lives in Munich - Kaufering is commutable. Internationally mobile, no visa sponsorship needed for Germany.</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>German is B1 (improving). SAP not on the CV. MSc runs to 12.2026 - confirm the role can wait for a 01.2027 start, or whether an earlier start is possible.</t>
-        </is>
-      </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Direct entry, permanent, full-time (no intake dates; Stepstone lists a home-office option)</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>Own the Financial Performance Management process for the Central Europe region: monthly and annual closings, rolling forecasts, cost controlling, business partnering; cross-functional and international projects. Explicitly the entry point of Hilti's CFO track - development via international assignments toward Group CFO-level roles.</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>Degree in Business Administration / Economics, ideally Finance / Controlling / Accounting focus; relevant internships and/or up to 3 years in a corporate finance function, audit firm or consulting; conceptual strength, stakeholder management, international ambition.</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Posting runs in English and German; German helps for DACH business partnering - ask Timur what level the team expects. Germany: no permit friction.</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>The literal 'CFO Track' entry role, and the reason this row stays on the sheet despite not being in the pasted list: direct entry (no intake window to miss), commutable from Munich, and the tightest match to the CV's FP&amp;A retune. A&amp;M restructuring covers the consulting/corporate-finance screen; KPI reporting and dashboards cover controlling &amp; reporting.</t>
+        </is>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>German B1; SAP not on the CV; confirm the role can wait for a 01.2027 start.</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t>Draft - verify posting</t>
         </is>
       </c>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>Confirm with Timur that this is the CFO-track entry role he means; check the posting is still live; confirm expected start date.</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>Decide whether to add it to the list Timur forwards - recommended. Confirm with him whether this is the route he calls 'the CFO track'.</t>
+        </is>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
         <is>
           <t>https://careers.hilti.group/en/jobs/16066-en/controller-m-f-d-international-finance-career-cfo-track/</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>careers.hilti.group + Stepstone #13672273, via search 31.08.2026. Note: 16512-de shows both 'Controller' and 'Senior Controller' titles in listings - check live.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="142.6" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Outperformer - Global Management Development Program, Finance Track (Germany)</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="O7" s="17" t="inlineStr">
+        <is>
+          <t>careers.hilti.group + Stepstone #13672273 via search 31.08.2026. 16512-de shows both 'Controller' and 'Senior Controller' titles in listings - check live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="79.59999999999999" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Global Trainee Program - Outperformer Operations Track (m/f/x)</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Your list</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>18688-en</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Hilti AG - Global HQ family, Schaan, Liechtenstein (m/f/x Schaan posting family)</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>24-month operations trainee program (fixed intake - confirm date)</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>12 months as Team Lead in a Plant or Tool Service Center (shopfloor coordination) or leading a production-technology project; then a 6-month Digitalization, Lean, Quality or Logistics project; then a 6-month international strategic project. Assessment Center at HQ in Liechtenstein.</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>Master's-level early-career profile; mobility; leadership potential. Likely leans toward engineering / supply-chain profiles - verify whether business/finance backgrounds are in scope.</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>English posting; German valuable on DACH shopfloors. PERMIT: same Schaan non-EU/EFTA warning as row 1.</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>Digital-operations evidence is real: AI agent workflows cutting reporting effort 60%, KPI dashboards, SQL/Python. Team-lead year matches the leadership record (Draycott, hackathon).</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>No plant or shopfloor exposure on the CV; the furthest of the finance-adjacent options from the CFO ambition; CH/LI permit.</t>
+        </is>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>Draft - verify posting</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="inlineStr">
+        <is>
+          <t>Keep only if genuinely drawn to operations - ask Timur whether an ops start still feeds a finance career at Hilti.</t>
+        </is>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>https://careers.hilti.group/en/jobs/18688-en/global-trainee-program-outperformer-operations-track-m-f-x/</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>careers.hilti.group via search 31.08.2026; structure from the Schaan operations-track family (46350-en). Verify live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="92.2" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Global Outperformer Graduate Programme (Business Track)</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Your list</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>16399-en</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Hilti Danmark - Copenhagen, Denmark</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>2-year Outperformer graduate programme</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>Rotations through roles and teams across the Danish business and internationally; mentoring by senior leaders; high-impact projects; the standard Outperformer summits and leadership journey with real responsibility from day one.</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>Master's; early-career profile; mobility; leadership potential. Posting in English.</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>English posting; Danish likely helpful for a customer-facing year - verify. PERMIT: Denmark needs its own work permit for non-EU citizens; a German residence permit does not transfer.</t>
+        </is>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>Strong English-language environment and the same graduate-program fit story; Copenhagen org is small and international.</t>
+        </is>
+      </c>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>DK permit if non-EU; Danish; the ID resolves to the business track, so the finance tie is indirect.</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>Draft - verify posting</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>Confirm which track the live posting recruits for (the ID resolves under both a generic and a business-track title) and the language/permit expectations.</t>
+        </is>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>https://careers.hilti.group/en/jobs/16399-en/global-outperformer-graduate-programme/</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>careers.hilti.group via search 31.08.2026 - 16399-en resolves to Copenhagen under two titles. Verify live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="117.4" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Outperformer - GMDP, Finance Track (Germany)</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Suggested</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>19572-de</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Hilti Deutschland AG - nationwide (BW, BY, BE, NRW listed); rotations incl. Kaufering hub + abroad</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>24-month global graduate program (fixed intake - confirm next intake date)</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>Option 1 rotation: 12 months Sales Account Manager in the home organisation (DE/AT/CH/NL), then 3 months finance project at home, 6 months Controlling &amp; Reporting at the Kaufering regional hub, 3 months finance project in another country. A second finance-track option exists. Includes an IMD Lausanne leadership qualification, a global summit at HQ in Schaan (LI) with Executive Board involvement, and a dedicated mentor.</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>Recent or soon-completing Master's. 6-30 months of initial professional experience (internships count). At least 6 months of international experience. Fluent English plus at least one other language. Globally mobile; leadership potential.</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>Fluent English + one other language required. Posting is in German - the 12-month DACH sales year very likely needs working German; confirm the expected level.</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr">
-        <is>
-          <t>Roughly 19 months of internships (A&amp;M 7 + TCG 6 + Biome 3 + SCAILE 3) - inside the 6-30 month window. International by construction: India -&gt; Portugal -&gt; Germany, plus a European Commission thesis. Languages: English, Hindi, Bengali fluent; German B1; basic Portuguese. Strong evidence for the account-manager year: owned North American clients and signed &gt;$100k ARR. Leadership: Draycott PE Challenge team lead, global AI hackathon organiser, UN Foundation.</t>
-        </is>
-      </c>
-      <c r="J5" s="15" t="inlineStr">
-        <is>
-          <t>Selling in a German-speaking market on B1 German is the main risk - ask how other internationals handled it. Intake timing vs 12.2026 graduation. Confirm whether Timur's own 'CFO track' means this program or the Kaufering controller route.</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>24-month rotational graduate program (German posting; fixed intake)</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Option 1: 12 months Sales Account Manager in the home organisation (DE/AT/CH/NL), 3 months finance project at home, 6 months Controlling &amp; Reporting at the Kaufering hub, 3 months finance project abroad. Option 2: Accounting &amp; Shared Services (3-6 mo) -&gt; Controlling &amp; Reporting (6-9 mo) -&gt; Credit &amp; Collection (3 mo). IMD Lausanne qualification; Schaan summit with the Executive Board.</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Recent Master's; 6-30 months initial professional experience; at least 6 months international experience; fluent English plus one other language; globally mobile.</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>German posting - working German for the DACH home organisation; B1 is the risk. Germany: no permit friction.</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>The finance track without the Schaan permit question: if CH/LI eligibility turns out to be a blocker for rows 1-2, this is the same program from German soil - and its option 2 skips the sales year.</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>German level; not in the pasted list (the -en postings suggest a preference for English environments - option 2's rotations are less language-exposed than a sales year).</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t>Draft - verify posting</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>Ask Timur which of the two paths he joined and which he'd recommend for Abir's profile; get intake dates and referral mechanics.</t>
-        </is>
-      </c>
-      <c r="M5" s="16" t="inlineStr">
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>Hold as the permit-safe fallback for the finance track; add to the list if Schaan eligibility is uncertain.</t>
+        </is>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
         <is>
           <t>https://careers.hilti.group/en/jobs/19572-de/global-management-development-program-outperformer-finance-track/</t>
         </is>
       </c>
-      <c r="N5" s="15" t="inlineStr">
+      <c r="O10" s="12" t="inlineStr">
         <is>
           <t>careers.hilti.group via search 31.08.2026 - verify live.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="54.4" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Finance Controller mit internationaler Entwicklungsperspektive (m/w/d)</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>wd-0033857-de; older twin 13232-de</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Hilti Deutschland AG - Kaufering (twin posting adds Oberhausen)</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Direct entry, permanent</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>Controlling role in the same Kaufering finance-hub family, positioned with an explicit international development perspective. Full description is on the live (German) posting.</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>Expected to mirror the CFO-track controller profile: business/economics degree with finance/controlling focus, early-career experience - verify on the live posting.</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>German-language posting - likely expects working German (B2+); confirm.</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>Same fit story as the CFO-Track Controller; a natural backup if 16066 is filled or on hold.</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>German level. May even be the same headcount as 16066 under a different title - clarify before listing both to Timur.</t>
-        </is>
-      </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>Draft - verify posting</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>Verify it is distinct from role #1; if yes, keep as backup on the list.</t>
-        </is>
-      </c>
-      <c r="M6" s="13" t="inlineStr">
-        <is>
-          <t>https://careers.hilti.group/en/jobs/wd-0033857-de/finance-controller-mit-internationaler-entwicklungsperspektive-m-w-d/</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>careers.hilti.group via search 31.08.2026 - verify live.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="54.4" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Outperformer - Global Management Trainee Program, Business Track (m/w/d)</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>57529-de; older listing 19157-de</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Hilti Deutschland AG - nationwide</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>Global graduate / trainee program</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>General-management twin of the finance track: sales-led rotations, international assignment, IMD leadership development - not finance-specialised.</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>Master's-level early-career profile; fluent English plus another language; global mobility; leadership potential - verify on the live posting.</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>German posting - German for the DACH sales rotations likely required.</t>
-        </is>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>Fallback only: uses Abir's commercial/GTM side (owned NA clients, &gt;$100k ARR) and keeps the Hilti door open, with a later internal move toward finance.</t>
-        </is>
-      </c>
-      <c r="J7" s="15" t="inlineStr">
-        <is>
-          <t>Not a finance role - weaker match to the CFO ambition. Only if the finance-track options don't work out.</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
+    <row r="11" ht="104.8" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>CFO Austria - development target: Global CFO career (m/f/x)</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Your list</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>19359-en</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Hilti Austria Ges.m.b.H - Vienna; member of the Executive Management Team</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Executive appointment - not an early-career role</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>Steer one of Hilti's most successful market organisations as its CFO: strategic decisions, business performance, people leadership - positioned to develop toward a global CFO career in the Group.</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>Master's in Finance/Business/Economics; strong finance leadership experience in an international environment (controlling, accounting; ideally corporate finance, audit or consulting background); proven FP&amp;A, performance-management and business-partnering track record; experience leading and developing high-performing teams.</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>Executive role in Austria - German near-certainly required; AT permit for non-EU citizens.</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>Honest read: not a viable application for a 12.2026 MSc graduate - it asks for years of finance leadership. Its value is as printed proof of where Hilti's CFO track leads.</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>The entire experience requirement.</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>On hold</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>Hold unless the finance options fall through.</t>
-        </is>
-      </c>
-      <c r="M7" s="16" t="inlineStr">
-        <is>
-          <t>https://careers.hilti.group/en/jobs/57529-de/global-management-trainee-program-outperformer-business-track-m-w-d/</t>
-        </is>
-      </c>
-      <c r="N7" s="15" t="inlineStr">
-        <is>
-          <t>careers.hilti.group via search 31.08.2026 - verify live.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="12" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="12" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="12" t="n"/>
+      <c r="M11" s="13" t="inlineStr">
+        <is>
+          <t>Do not apply. Use it in the Timur conversation instead: 'this is where I want the track to take me - which entry door would you pick today?'</t>
+        </is>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>https://careers.hilti.group/en/jobs/19359-en/cfo-austria-with-development-target-to-global-cfo-career-m-f-x/</t>
+        </is>
+      </c>
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t>careers.hilti.group via search 31.08.2026. Verify live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="13" t="n"/>
+      <c r="J12" s="13" t="n"/>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="13" t="n"/>
+      <c r="O12" s="13" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
+      <c r="J13" s="13" t="n"/>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="13" t="n"/>
+      <c r="N13" s="13" t="n"/>
+      <c r="O13" s="13" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="13" t="n"/>
+      <c r="J14" s="13" t="n"/>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="13" t="n"/>
+      <c r="O14" s="13" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="13" t="n"/>
+      <c r="O15" s="13" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N40"/>
+  <autoFilter ref="A3:O40"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K4:K40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L4:L40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft - verify posting,Shortlisted,Sent to Timur,Applied,Interview,Offer,Closed - Rejected,On hold"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -1261,39 +1633,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Screening criteria -&gt; evidence map (for the Timur message and interview prep)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>What Hilti screens on</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Applies to</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Abir's evidence</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Where it sits on the CV</t>
         </is>
@@ -1305,39 +1677,39 @@
           <t>Master's in Finance / business degree with finance-controlling focus</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>All roles</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>MSc Finance, Nova SBE (FT #8), top 10% of class; BMS in Finance &amp; Strategy, magna cum laude, top 10%</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
     </row>
     <row r="5" ht="41.8" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Experience window: internships and/or up to 3 yrs (Controller); 6-30 months (Outperformer)</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Experience window: 6-30 months (programs); internships / up to 3 yrs (Controller)</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>All early-career roles</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>~19 months across A&amp;M (7), TCG (6), Biome (3), SCAILE (3) - inside both windows</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Work Experience dates</t>
         </is>
@@ -1349,39 +1721,39 @@
           <t>Corporate finance / audit / consulting background</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Controller</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Finance tracks, Controller</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>A&amp;M restructuring: Fortune 500 clients, &gt;$100M debt and leases, U.S. Chapter 11; TCG boutique strategy consulting</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>A&amp;M and TCG entries</t>
         </is>
       </c>
     </row>
     <row r="7" ht="41.8" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>FP&amp;A toolkit: closings, rolling forecasts, cost controlling</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>Controller</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Finance tracks, Controller</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Scenario models behind a $9.8M risk-mitigation plan; EBITDA sensitivity across liquidity and supplier scenarios; automated weekly KPI reporting (manual effort -60%); KPI dashboards</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>A&amp;M + SCAILE bullets; Focus areas row</t>
         </is>
@@ -1393,39 +1765,39 @@
           <t>Business partnering and stakeholder management</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>All roles</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Informed board-level decisions; prepared creditor-negotiation presentations for client leadership; led 90+ stakeholder interviews; first point of contact for North American clients</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>A&amp;M, TCG, SCAILE bullets</t>
         </is>
       </c>
     </row>
     <row r="9" ht="29.2" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>At least 6 months of international experience</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>Outperformer</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Outperformer programs</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>India (work) -&gt; Portugal (MSc) -&gt; Germany (work); Master's thesis with the European Commission across EU member states</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Whole page</t>
         </is>
@@ -1437,127 +1809,149 @@
           <t>Global mobility</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>All roles</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>'Internationally mobile' stated in the header; has already moved countries twice for study and work</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Header line</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="29.2" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Fluent English + at least one other language</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Outperformer</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>English, Hindi, Bengali fluent; German B1 and improving; basic Portuguese</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Languages row</t>
+    <row r="11" ht="79.59999999999999" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Work authorisation, by location</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Varies by row</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Germany: no visa sponsorship required (per prior CVs - confirm current permit type). Liechtenstein/Switzerland (Schaan rows), Denmark, Austria: separate permits; Hilti's Schaan trainee postings require non-EU/EFTA applicants to declare eligibility. ACTION: confirm citizenship and permit facts before anything is forwarded.</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Header line (scoped to Germany)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="29.2" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Customer-facing capability (12-month Account Manager rotation)</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Outperformer</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
+          <t>Fluent English + at least one other language</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Outperformer programs</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>English, Hindi, Bengali fluent; German B1 and improving; basic Portuguese</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Languages row</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="29.2" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Customer-facing capability (Account Manager rotation)</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Business + finance tracks</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Owned North American clients as first point of contact; signed and onboarded &gt;$100k ARR</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>SCAILE bullets</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="41.8" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="14" ht="41.8" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Operations / digital-operations capability</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Operations track</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>AI agent workflows cutting manual reporting effort 60%; KPI dashboards; Power BI, SQL, Python. Gap to own: no plant or shopfloor exposure on the page</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>SCAILE bullets + Technical row</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="41.8" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Leadership potential</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>All roles</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Team Lead, Draycott Private Equity Challenge; organiser of a 24-hour global AI hackathon (MIT Sloan AI Club x TUM); UN Foundation campaigns for 1,200+ women and children</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Education + Extracurricular</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="29.2" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Digital / analytics edge</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Power BI, SQL, Python; AI agent workflows that cut reporting effort 60%; GenAI visibility dashboards</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Technical row + SCAILE bullets</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="41.8" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="16" ht="54.4" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Gaps to manage proactively</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>German B1 (name the trajectory: B2 course, timeline); 08.2024-07.2025 gap between degrees (have the answer ready); SAP not evidenced; availability from 01.2027 to confirm</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>German B1 (name the trajectory: course, timeline to B2); 08.2024-07.2025 gap between degrees (have the answer ready); SAP not evidenced; availability from 01.2027 to confirm; CH/LI + DK permit status to establish</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
